--- a/Data/EXCEL/Transfer/salemon/202412/8179-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/8179-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BC9FC08-E8F1-4AFD-85FA-D4E18245D3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB9CA8FB-DB14-41D6-AD14-516B267AC609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{CAA4B751-590F-438B-B27E-0931EE4D0277}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{084340E5-6926-4E15-920D-F298F735D081}"/>
   </bookViews>
   <sheets>
     <sheet name="8179-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1255,21 +1255,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7450F2D9-7409-4548-AB98-ACC60AD66DE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6898122A-6321-4FFF-ADEF-AB264671716E}">
   <dimension ref="A1:Q19"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7265625" customWidth="1"/>
-    <col min="2" max="5" width="14.54296875" customWidth="1"/>
-    <col min="6" max="7" width="16" customWidth="1"/>
-    <col min="8" max="10" width="13.81640625" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" customWidth="1"/>
-    <col min="12" max="15" width="13.81640625" customWidth="1"/>
-    <col min="16" max="16" width="14.54296875" customWidth="1"/>
-    <col min="17" max="17" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.875" customWidth="1"/>
+    <col min="8" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1296,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1378,7 +1378,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1417,7 +1417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>44866</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>-27.8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>44835</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>-24.9</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>44805</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>-21.6</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>44774</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>-17.399999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>44743</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>-12.1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>44713</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>-7.45</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>44682</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>-6.75</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>44652</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>-4.7</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>44621</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>-1.39</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>44593</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>44562</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>44531</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>44501</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>44470</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>44440</v>
       </c>
